--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6FF1A2-D1A7-43E0-9AC6-C0ECA9D9A830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E706EE32-2EFB-4F61-BA62-1041048EDAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_effect_display_v8" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -205,6 +205,14 @@
   </si>
   <si>
     <t>fang_bao</t>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu_mian</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -546,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -770,6 +778,30 @@
         <v>35</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_display_v8【迷宫-技能-效果展示信息】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E706EE32-2EFB-4F61-BA62-1041048EDAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74057853-5081-4AEC-96F2-52AB6B572AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_effect_display_v8" sheetId="1" r:id="rId1"/>
@@ -207,11 +207,11 @@
     <t>fang_bao</t>
   </si>
   <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>bu_mian</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复生命</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
